--- a/parameterSweep.xlsx
+++ b/parameterSweep.xlsx
@@ -1688,7 +1688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="H1:W113"/>
+  <dimension ref="H1:W234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.05"/>
   <sheetData>
     <row r="1" ht="105.4" customHeight="1" thickBot="1">
@@ -6834,6 +6834,6661 @@
         <v/>
       </c>
     </row>
+    <row r="114">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-19-19_159224</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>777001</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>21,18</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>8</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P114" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>grounding/mixed66-96_seed1.pth</t>
+        </is>
+      </c>
+      <c r="R114" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V114">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-19-19_159224\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W114">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-19-19_159224\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-45-23_388972</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>4004</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>12</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R115" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V115">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-45-23_388972\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W115">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-45-23_388972\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-45-23_389109</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>5005</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>12</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R116" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V116">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-45-23_389109\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W116">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-45-23_389109\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-45-35_826931</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>6006</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>12</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R117" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V117">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-45-35_826931\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W117">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-45-35_826931\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-45-35_827526</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>12</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P118" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R118" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V118">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-45-35_827526\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W118">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-45-35_827526\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-46-10_390244</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>1001</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>12</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P119" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R119" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V119">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-46-10_390244\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W119">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-46-10_390244\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-47-04_828303</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>3003</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>12</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R120" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V120">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-47-04_828303\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W120">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-47-04_828303\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-50-25_3700228</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>4004</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>12</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P121" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V121">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-50-25_3700228\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W121">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-50-25_3700228\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_01-50-25_3700306</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>5005</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>12</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P122" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R122" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V122">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-50-25_3700306\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W122">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_01-50-25_3700306\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_08-06-30_415513</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>6006</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>12</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P123" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V123">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-06-30_415513\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W123">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-06-30_415513\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_08-12-37_854157</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>12</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P124" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V124">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-12-37_854157\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W124">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-12-37_854157\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_08-17-36_3882751</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1001</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>12</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O125" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V125">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-17-36_3882751\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W125">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-17-36_3882751\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_08-18-49_855414</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>3003</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>12</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O126" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P126" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R126" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V126">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-18-49_855414\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W126">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-18-49_855414\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_08-32-31_418941</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>4004</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>12</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O127" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V127">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-32-31_418941\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W127">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-32-31_418941\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_08-35-37_856813</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>5005</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>12</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O128" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P128" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V128">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-35-37_856813\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W128">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-35-37_856813\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_08-41-36_3884575</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>6006</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>12</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V129">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-41-36_3884575\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W129">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-41-36_3884575\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_08-47-54_420595</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>1001</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>12</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O130" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P130" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R130" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V130">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-47-54_420595\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W130">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_08-47-54_420595\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_15-07-14_445735</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>12</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O131" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P131" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R131" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V131">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-07-14_445735\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W131">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-07-14_445735\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_15-25-33_3911366</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>3003</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>12</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O132" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V132">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-25-33_3911366\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W132">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-25-33_3911366\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_15-26-23_3912066</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>4004</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>12</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V133">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-26-23_3912066\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W133">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-26-23_3912066\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_15-28-53_885563</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>6006</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>12</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O134" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P134" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R134" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V134">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-28-53_885563\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W134">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-28-53_885563\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_15-30-55_886418</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>1001</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>12</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P135" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R135" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V135">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-30-55_886418\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W135">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-30-55_886418\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_15-41-11_448860</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>12</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O136" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P136" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R136" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V136">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-41-11_448860\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W136">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-41-11_448860\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_15-53-48_3915772</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>3003</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>12</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P137" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R137" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V137">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-53-48_3915772\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W137">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_15-53-48_3915772\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_19-13-01_3929851</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>460101</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O138" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P138" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V138">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_19-13-01_3929851\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W138">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_19-13-01_3929851\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_19-13-01_467025</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>5050</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O139" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R139" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V139">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_19-13-01_467025\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W139">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_19-13-01_467025\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_19-13-01_901712</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>22222222</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O140" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P140" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R140" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V140">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_19-13-01_901712\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W140">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_19-13-01_901712\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-45-14_2201297</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>546564</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O141" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P141" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R141" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V141">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-45-14_2201297\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W141">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-45-14_2201297\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-45-30_4178960</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>468</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O142" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R142" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V142">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-45-30_4178960\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W142">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-45-30_4178960\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-46-00_3966205</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>1841</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O143" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P143" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R143" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V143">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-46-00_3966205\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W143">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-46-00_3966205\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-47-11_4184388</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>84846464</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O144" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P144" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R144" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V144">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-47-11_4184388\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W144">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-47-11_4184388\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-47-12_1072256</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>6856924</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P145" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V145">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-47-12_1072256\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W145">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-47-12_1072256\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-48-10_1074248</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>314159265</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O146" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P146" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R146" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V146">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-48-10_1074248\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W146">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-48-10_1074248\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-49-17_2235803</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>4</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O147" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P147" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R147" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V147">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-49-17_2235803\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W147">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-49-17_2235803\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-49-17_2688</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>6</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O148" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P148" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R148" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V148">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-49-17_2688\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W148">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-49-17_2688\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-49-47_1672344</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>5</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O149" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P149" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V149">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-49-47_1672344\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W149">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-49-47_1672344\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-51-47_2207626</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>4684157</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O150" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P150" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R150" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V150">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-51-47_2207626\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W150">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-51-47_2207626\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-54-53_1288792</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>564184</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O151" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P151" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V151">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-54-53_1288792\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W151">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-54-53_1288792\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-56-59_1699958</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>478</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O152" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P152" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R152" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V152">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-56-59_1699958\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W152">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-56-59_1699958\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-56-59_1699959</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>3463475368</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O153" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P153" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R153" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V153">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-56-59_1699959\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W153">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-56-59_1699959\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-58-51_4001941</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>55376</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O154" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P154" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R154" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V154">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-58-51_4001941\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W154">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-58-51_4001941\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-24_23-58-52_1342286</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>64352663</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P155" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R155" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V155">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-58-52_1342286\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W155">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-24_23-58-52_1342286\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_00-25-04_3423577</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>6553</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P156" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R156" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V156">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_00-25-04_3423577\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W156">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_00-25-04_3423577\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_00-28-17_1846618</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>10100101</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P157" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R157" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V157">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_00-28-17_1846618\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W157">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_00-28-17_1846618\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_00-29-37_1857095</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>202020</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P158" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V158">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_00-29-37_1857095\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W158">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_00-29-37_1857095\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_00-30-22_1861746</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>303030</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P159" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V159">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_00-30-22_1861746\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W159">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_00-30-22_1861746\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-20-12_1998550</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>54851638</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P160" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R160" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V160">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-20-12_1998550\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W160">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-20-12_1998550\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-21-17_391983</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>65312321</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P161" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R161" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V161">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-21-17_391983\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W161">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-21-17_391983\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-22-18_2842268</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>25925907</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P162" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R162" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V162">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-22-18_2842268\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W162">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-22-18_2842268\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-36-23_4040792</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>710936838</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>mlp</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P163" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R163" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V163">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-36-23_4040792\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W163">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-36-23_4040792\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-38-33_67307</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>546564</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P164" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R164" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V164">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-38-33_67307\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W164">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-38-33_67307\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-38-49_1447335</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>619864265</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>mlp</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P165" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R165" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V165">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-38-49_1447335\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W165">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-38-49_1447335\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-42-55_2807283</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>442109015</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>mlp</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P166" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V166">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-42-55_2807283\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W166">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-42-55_2807283\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-48-29_716059</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>397755542</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>mlp</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P167" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R167" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V167">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-48-29_716059\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W167">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-48-29_716059\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_01-54-43_807373</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>403851061</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>mlp</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P168" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R168" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V168">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-54-43_807373\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W168">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_01-54-43_807373\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_02-20-11_2818149</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>468</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P169" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R169" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V169">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_02-20-11_2818149\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W169">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_02-20-11_2818149\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_10-29-46_963285</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>466555</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P170" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R170" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V170">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_10-29-46_963285\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W170">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_10-29-46_963285\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_20-43-47_1001371</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>34653545</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P171" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R171" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V171">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_20-43-47_1001371\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W171">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_20-43-47_1001371\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_20-43-47_4025676</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>34645628</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P172" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R172" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V172">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_20-43-47_4025676\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W172">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_20-43-47_4025676\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-25_20-43-47_559273</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>34661465</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P173" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R173" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V173">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_20-43-47_559273\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W173">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-25_20-43-47_559273\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-06-23_1057221</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>34732735</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P174" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R174" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V174">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-06-23_1057221\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W174">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-06-23_1057221\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-06-23_615504</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>34740655</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P175" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R175" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V175">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-06-23_615504\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W175">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-06-23_615504\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-06-36_4085276</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>34724818</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P176" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R176" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V176">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-06-36_4085276\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W176">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-06-36_4085276\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-16_898255</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>65312321</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P177" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R177" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V177">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-16_898255\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W177">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-16_898255\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-16_898256</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>54851638</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P178" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R178" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V178">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-16_898256\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W178">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-16_898256\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-16_898308</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>25925907</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P179" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R179" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V179">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-16_898308\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W179">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-16_898308\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_1731002</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>1841</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P180" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R180" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V180">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_1731002\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W180">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_1731002\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_2491993</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>6856924</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P181" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R181" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V181">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2491993\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W181">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2491993\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_2491994</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>84846464</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P182" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R182" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V182">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2491994\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W182">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2491994\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_2492036</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>314159265</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P183" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R183" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V183">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2492036\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W183">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2492036\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_2804477</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>4684157</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P184" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R184" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V184">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2804477\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W184">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2804477\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_2804482</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>3256041463</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P185" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R185" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V185">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2804482\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W185">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2804482\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_2804511</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>564184</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P186" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R186" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V186">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2804511\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W186">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_2804511\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_3561444</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>55376</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P187" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R187" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V187">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_3561444\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W187">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_3561444\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_3561445</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>64352663</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O188" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P188" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R188" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V188">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_3561445\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W188">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_3561445\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-29-41_3561477</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>6553</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O189" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P189" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R189" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V189">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_3561477\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W189">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-29-41_3561477\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-13_2493425</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>4</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O190" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P190" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R190" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V190">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-13_2493425\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W190">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-13_2493425\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-13_3488014</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>546564</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O191" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P191" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R191" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V191">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-13_3488014\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W191">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-13_3488014\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-13_608744</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>468</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P192" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R192" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V192">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-13_608744\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W192">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-13_608744\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-31_2806171</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>3463475368</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O193" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P193" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R193" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V193">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-31_2806171\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W193">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-31_2806171\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-31_3563137</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>10100101</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P194" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R194" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V194">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-31_3563137\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W194">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-31_3563137\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-38_2806614</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>478</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P195" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R195" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V195">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-38_2806614\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W195">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-38_2806614\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-38_2806615</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>1785812914</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O196" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P196" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R196" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V196">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-38_2806615\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W196">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-38_2806615\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-38_3563526</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>303030</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O197" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P197" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R197" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V197">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-38_3563526\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W197">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-38_3563526\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-38_3563527</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>202020</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O198" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P198" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R198" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V198">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-38_3563527\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W198">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-38_3563527\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-30-39_2493943</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>5</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>12,6</t>
+        </is>
+      </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O199" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P199" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R199" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V199">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-39_2493943\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W199">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-30-39_2493943\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_13-31-06_2494245</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>6</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>15,3</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O200" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P200" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R200" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V200">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-31-06_2494245\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W200">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_13-31-06_2494245\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_20-36-07_1077617</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>34883196</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>3,27</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O201" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P201" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R201" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V201">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_20-36-07_1077617\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W201">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_20-36-07_1077617\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_20-36-07_636968</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>34891116</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>5,15</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O202" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P202" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R202" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V202">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_20-36-07_636968\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W202">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_20-36-07_636968\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-26_20-36-08_4106178</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>34875279</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>3,27</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O203" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P203" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R203" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V203">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_20-36-08_4106178\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W203">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-26_20-36-08_4106178\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-42_1172807</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>3141592</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>8</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O204" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P204" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R204" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V204">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-42_1172807\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W204">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-42_1172807\search_9_6_seed_3141592_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-42_1172833</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>2718281</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>8</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O205" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P205" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R205" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V205">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-42_1172833\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W205">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-42_1172833\search_9_6_seed_2718281_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-42_1172859</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>1618033</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>8</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O206" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P206" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R206" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V206">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-42_1172859\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W206">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-42_1172859\search_9_6_seed_1618033_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-44_1172885</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>1414213</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>8</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O207" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P207" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R207" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V207">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-44_1172885\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W207">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-44_1172885\search_9_6_seed_1414213_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-47_1172914</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1732050</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>8</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O208" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P208" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R208" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V208">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-47_1172914\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W208">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-47_1172914\search_9_6_seed_1732050_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-51_1172941</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>2236067</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>8</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O209" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P209" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R209" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V209">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-51_1172941\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W209">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-51_1172941\search_9_6_seed_2236067_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-54_1173000</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>2645751</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>8</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O210" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P210" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R210" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V210">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-54_1173000\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W210">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-54_1173000\search_9_6_seed_2645751_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-56_1173035</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>3316624</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>8</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O211" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P211" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R211" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V211">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-56_1173035\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W211">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-56_1173035\search_9_6_seed_3316624_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-48-59_1173071</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>1234567</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>8</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O212" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P212" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R212" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V212">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-59_1173071\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W212">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-48-59_1173071\search_9_6_seed_1234567_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-49-02_1173109</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>7654321</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>8</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O213" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P213" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R213" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V213">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-49-02_1173109\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W213">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-49-02_1173109\search_9_6_seed_7654321_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-49-05_1173144</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>9876543</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>8</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O214" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P214" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R214" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V214">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-49-05_1173144\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W214">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-49-05_1173144\search_9_6_seed_9876543_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-49-09_1173179</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>1111111</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>8</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O215" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P215" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>2026-07-12_20-18-32/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R215" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V215">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-49-09_1173179\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W215">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-49-09_1173179\search_9_6_seed_1111111_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-10_734813</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>3141592</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K216" t="n">
+        <v>8</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O216" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P216" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R216" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V216">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-10_734813\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W216">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-10_734813\search_9_6_seed_3141592_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-10_734850</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>2718281</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>8</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O217" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P217" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R217" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V217">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-10_734850\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W217">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-10_734850\search_9_6_seed_2718281_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-10_734883</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>1618033</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>8</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O218" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P218" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R218" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V218">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-10_734883\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W218">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-10_734883\search_9_6_seed_1618033_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-13_734914</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>1414213</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>8</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O219" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P219" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R219" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V219">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-13_734914\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W219">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-13_734914\search_9_6_seed_1414213_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-16_734943</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>1732050</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>8</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O220" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P220" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R220" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V220">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-16_734943\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W220">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-16_734943\search_9_6_seed_1732050_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-20_734978</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>2236067</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>8</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O221" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P221" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R221" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V221">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-20_734978\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W221">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-20_734978\search_9_6_seed_2236067_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-23_735045</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>2645751</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>8</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O222" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P222" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R222" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V222">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-23_735045\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W222">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-23_735045\search_9_6_seed_2645751_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-26_735091</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>3316624</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>8</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O223" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P223" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R223" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V223">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-26_735091\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W223">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-26_735091\search_9_6_seed_3316624_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-28_735131</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>1234567</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>8</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O224" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P224" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R224" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V224">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-28_735131\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W224">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-28_735131\search_9_6_seed_1234567_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-32_735172</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>7654321</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>8</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O225" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P225" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R225" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V225">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-32_735172\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W225">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-32_735172\search_9_6_seed_7654321_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/2026-07-27_21-50-34_735210</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>9876543</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>8</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O226" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P226" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R226" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V226">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-34_735210\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W226">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\2026-07-27_21-50-34_735210\search_9_6_seed_9876543_experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/truncated_matrixA\2026-07-23_16-39-33_352442</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>12</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O227" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P227" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R227" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V227">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_16-39-33_352442\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W227">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_16-39-33_352442\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/truncated_matrixA\2026-07-23_17-04-44_790643</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>3003</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>12</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O228" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P228" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R228" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V228">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-04-44_790643\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W228">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-04-44_790643\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/truncated_matrixA\2026-07-23_17-06-26_355068</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>4004</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K229" t="n">
+        <v>12</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O229" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P229" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R229" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V229">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-06-26_355068\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W229">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-06-26_355068\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/truncated_matrixA\2026-07-23_17-26-23_3831930</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>5005</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>12</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O230" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P230" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R230" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V230">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-26-23_3831930\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W230">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-26-23_3831930\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/truncated_matrixA\2026-07-23_17-30-12_792942</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>6006</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>12</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O231" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P231" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R231" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V231">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-30-12_792942\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W231">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-30-12_792942\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/truncated_matrixA\2026-07-23_17-38-01_3833038</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>1001</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>12</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O232" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R232" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V232">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-38-01_3833038\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W232">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_17-38-01_3833038\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/truncated_matrixA\2026-07-23_18-06-16_3835747</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>12</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O233" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R233" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V233">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_18-06-16_3835747\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W233">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_18-06-16_3835747\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/truncated_matrixA\2026-07-23_22-38-48_814037</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>3003</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>12</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O234" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>2026-07-12_21-15-58/surrogate_6x6.pth</t>
+        </is>
+      </c>
+      <c r="R234" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V234">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_22-38-48_814037\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W234">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\truncated_matrixA\2026-07-23_22-38-48_814037\experiment.txt","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/parameterSweep.xlsx
+++ b/parameterSweep.xlsx
@@ -1689,7 +1689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="H1:W102"/>
+  <dimension ref="H1:W135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.05"/>
   <cols>
     <col width="26" bestFit="1" customWidth="1" min="8" max="8"/>
@@ -7203,6 +7203,1821 @@
         <v/>
       </c>
     </row>
+    <row r="103">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-40_1417601</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>90210</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>8</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R103" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V103">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-40_1417601\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W103">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-40_1417601\experiment_9_6_seed_90210","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-40_1417629</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>466555</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>8</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P104" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R104" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V104">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-40_1417629\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W104">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-40_1417629\experiment_9_6_seed_466555","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-40_1417662</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>460101</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>8</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P105" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R105" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V105">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-40_1417662\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W105">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-40_1417662\experiment_9_6_seed_460101","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-42_1417690</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>7134066</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>8</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P106" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R106" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V106">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-42_1417690\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W106">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-42_1417690\experiment_9_6_seed_7134066","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-42_1924827</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>90210</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>8</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P107" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R107" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V107">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-42_1924827\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W107">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-42_1924827\experiment_9_6_seed_90210","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-42_1924859</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>466555</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>8</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P108" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V108">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-42_1924859\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W108">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-42_1924859\experiment_9_6_seed_466555","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-42_1924887</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>460101</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>8</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P109" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R109" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V109">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-42_1924887\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W109">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-42_1924887\experiment_9_6_seed_460101","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-45_1924915</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>7134066</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>8</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P110" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R110" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V110">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-45_1924915\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W110">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-45_1924915\experiment_9_6_seed_7134066","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-46_1417727</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>999</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>8</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R111" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V111">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-46_1417727\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W111">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-46_1417727\experiment_9_6_seed_999","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-51_1924950</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>999</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>8</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P112" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R112" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V112">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-51_1924950\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W112">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-51_1924950\experiment_9_6_seed_999","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-52_1417760</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>67</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>8</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P113" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R113" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V113">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-52_1417760\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W113">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-52_1417760\experiment_9_6_seed_67","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-56-54_1925040</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>67</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>8</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P114" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R114" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V114">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-54_1925040\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W114">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-56-54_1925040\experiment_9_6_seed_67","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-57-21_692662</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>90210</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>8</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H4_s4000.pth</t>
+        </is>
+      </c>
+      <c r="R115" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V115">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692662\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W115">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692662\experiment_9_6_seed_90210","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-57-21_692690</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>466555</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>8</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P116" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H4_s4000.pth</t>
+        </is>
+      </c>
+      <c r="R116" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V116">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692690\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W116">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692690\experiment_9_6_seed_466555","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-57-21_692715</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>460101</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>8</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P117" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H4_s4000.pth</t>
+        </is>
+      </c>
+      <c r="R117" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V117">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692715\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W117">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692715\experiment_9_6_seed_460101","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-57-21_692746</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>7134066</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>8</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P118" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H4_s4000.pth</t>
+        </is>
+      </c>
+      <c r="R118" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V118">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692746\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W118">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692746\experiment_9_6_seed_7134066","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-57-21_692774</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>999</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>8</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P119" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H4_s4000.pth</t>
+        </is>
+      </c>
+      <c r="R119" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V119">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692774\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W119">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692774\experiment_9_6_seed_999","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_11-57-21_692801</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>67</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>8</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H4_s4000.pth</t>
+        </is>
+      </c>
+      <c r="R120" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V120">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692801\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W120">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_11-57-21_692801\experiment_9_6_seed_67","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_16-46-23_3905732</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>7134066</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>8</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P121" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V121">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_16-46-23_3905732\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W121">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_16-46-23_3905732\experiment_9_6_seed_7134066_unfreeze_at_50","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_16-47-28_3955272</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>7134066</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>8</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P122" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R122" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V122">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_16-47-28_3955272\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W122">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_16-47-28_3955272\experiment_9_6_seed_7134066_unfreeze_at_100","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-05_16-48-52_4003461</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>7134066</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>8</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P123" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H6_s3000.pth</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V123">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_16-48-52_4003461\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W123">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-05_16-48-52_4003461\experiment_9_6_seed_7134066_unfreeze_at_200","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-02-16_2002194</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>90210</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>8</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P124" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H10_s2000.pth</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V124">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-16_2002194\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W124">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-16_2002194\experiment_9_6_seed_90210","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-02-16_2002221</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>466555</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>8</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O125" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H10_s2000.pth</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V125">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-16_2002221\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W125">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-16_2002221\experiment_9_6_seed_466555","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-02-16_2002254</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>460101</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>8</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O126" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P126" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H10_s2000.pth</t>
+        </is>
+      </c>
+      <c r="R126" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V126">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-16_2002254\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W126">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-16_2002254\experiment_9_6_seed_460101","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-02-16_2002285</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>7134066</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>8</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O127" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H10_s2000.pth</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V127">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-16_2002285\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W127">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-16_2002285\experiment_9_6_seed_7134066","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-02-17_2002313</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>999</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>8</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O128" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P128" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H10_s2000.pth</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V128">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-17_2002313\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W128">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-17_2002313\experiment_9_6_seed_999","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-02-21_2002340</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>67</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>8</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H10_s2000.pth</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V129">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-21_2002340\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W129">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-02-21_2002340\experiment_9_6_seed_67","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-20-52_1495640</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>90210</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>8</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O130" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P130" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R130" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V130">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-20-52_1495640\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W130">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-20-52_1495640\experiment_9_6_seed_90210","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-20-53_1495667</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>466555</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>8</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O131" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P131" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R131" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V131">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-20-53_1495667\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W131">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-20-53_1495667\experiment_9_6_seed_466555","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-20-56_1495696</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>460101</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>8</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O132" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V132">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-20-56_1495696\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W132">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-20-56_1495696\experiment_9_6_seed_460101","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-21-00_1495728</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>7134066</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>8</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V133">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-21-00_1495728\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W133">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-21-00_1495728\experiment_9_6_seed_7134066","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-21-04_1495802</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>999</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>8</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O134" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P134" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R134" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V134">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-21-04_1495802\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W134">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-21-04_1495802\experiment_9_6_seed_999","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>c:/users/omer/rl-qecc-data/reinforcementLearning\2026-08-06_03-21-07_1495859</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>67</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>8</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P135" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>sweep2/g5_mix_66-96_H7_s54321.pth</t>
+        </is>
+      </c>
+      <c r="R135" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="V135">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-21-07_1495859\postProcessing.png","plot")</f>
+        <v/>
+      </c>
+      <c r="W135">
+        <f>HYPERLINK("c:\users\omer\rl-qecc-data\reinforcementLearning\2026-08-06_03-21-07_1495859\experiment_9_6_seed_67","experiment.txt")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
